--- a/Excel/FoodConfig.xlsx
+++ b/Excel/FoodConfig.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -483,89 +483,285 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>item_potion_red</t>
+          <t>food_carrot_soup</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>生命药水</t>
+          <t>胡萝卜暖汤</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="D3" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>[item_gold]</t>
+          <t>[ingredient_carrot,ingredient_salt]</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>[10]</t>
+          <t>[2,1]</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>food_carrot_soup</t>
+          <t>food_mushroom_skewer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>胡萝卜汤</t>
+          <t>迷雾蘑菇串</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="D4" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>[ingredient_carrot,ingredient_salt]</t>
+          <t>[ingredient_mushroom,ingredient_salt]</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>[2,1]</t>
+          <t>[3,1]</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>food_meat_stew</t>
+          <t>food_lotus_crisp</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>炖肉</t>
+          <t>莲藕脆片</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="D5" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>[ingredient_meat,ingredient_salt]</t>
+          <t>[ingredient_lotus_root,ingredient_salt]</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>[2,1]</t>
+          <t>[3,1]</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
+        <is>
+          <t>food_spiced_egg</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>香料煎蛋</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>95</v>
+      </c>
+      <c r="D6" t="n">
+        <v>22</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>[ingredient_egg,ingredient_spice]</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>[2,1]</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>food_wheat_cake</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>麦香烤饼</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>90</v>
+      </c>
+      <c r="D7" t="n">
+        <v>20</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>[ingredient_wheat,ingredient_honey]</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>[2,1]</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>food_fish_rice</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>河鲜饭团</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>130</v>
+      </c>
+      <c r="D8" t="n">
+        <v>35</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>[ingredient_fish,ingredient_rice,ingredient_salt]</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>[1,2,1]</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>food_honey_milk</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>蜂蜜热奶</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>120</v>
+      </c>
+      <c r="D9" t="n">
+        <v>45</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>[ingredient_milk,ingredient_honey]</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>[2,1]</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>food_meat_stew</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>秘境炖肉</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>150</v>
+      </c>
+      <c r="D10" t="n">
+        <v>40</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>[ingredient_meat,ingredient_carrot,ingredient_spice]</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>[2,1,1]</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>food_maze_bento</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>探险便当</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>220</v>
+      </c>
+      <c r="D11" t="n">
+        <v>65</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>[ingredient_rice,ingredient_meat,ingredient_egg,ingredient_carrot]</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>[2,1,1,1]</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>food_feast_platter</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>迷宫丰收拼盘</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>360</v>
+      </c>
+      <c r="D12" t="n">
+        <v>100</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>[ingredient_meat,ingredient_fish,ingredient_mushroom,ingredient_spice,ingredient_honey]</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>[2,2,2,1,1]</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>END</t>
         </is>
